--- a/frontend/public/templates/scores/v1/teaching-g23-students.xlsx
+++ b/frontend/public/templates/scores/v1/teaching-g23-students.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入数据" sheetId="1" r:id="Rca8c3cf8c5534438"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入数据" sheetId="1" r:id="R7793c288c3cd49c7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,10 +13,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="3">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0.##"/>
     <x:numFmt numFmtId="201" formatCode="@"/>
-    <x:numFmt numFmtId="202" formatCode="0"/>
+    <x:numFmt numFmtId="202" formatCode="0.00%"/>
+    <x:numFmt numFmtId="203" formatCode="0"/>
   </x:numFmts>
   <x:fonts count="4">
     <x:font>
@@ -70,7 +71,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="16">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -100,10 +101,16 @@
     <x:xf numFmtId="202" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="201" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="202" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -315,6 +322,7 @@
     <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
@@ -330,318 +338,373 @@
       <x:c r="D1" s="8" t="str">
         <x:v>等级分数</x:v>
       </x:c>
+      <x:c r="E1" s="8" t="str">
+        <x:v>年级百分比</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="25" customHeight="1">
-      <x:c r="A2" s="11"/>
-      <x:c r="B2" s="11"/>
-      <x:c r="C2" s="12"/>
-      <x:c r="D2" s="13"/>
+      <x:c r="A2" s="12"/>
+      <x:c r="B2" s="12"/>
+      <x:c r="C2" s="13"/>
+      <x:c r="D2" s="14"/>
+      <x:c r="E2" s="15"/>
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
-      <x:c r="A3" s="11"/>
-      <x:c r="B3" s="11"/>
-      <x:c r="C3" s="12"/>
-      <x:c r="D3" s="13"/>
+      <x:c r="A3" s="12"/>
+      <x:c r="B3" s="12"/>
+      <x:c r="C3" s="13"/>
+      <x:c r="D3" s="14"/>
+      <x:c r="E3" s="15"/>
     </x:row>
     <x:row r="4" ht="25" customHeight="1">
-      <x:c r="A4" s="11"/>
-      <x:c r="B4" s="11"/>
-      <x:c r="C4" s="12"/>
-      <x:c r="D4" s="13"/>
+      <x:c r="A4" s="12"/>
+      <x:c r="B4" s="12"/>
+      <x:c r="C4" s="13"/>
+      <x:c r="D4" s="14"/>
+      <x:c r="E4" s="15"/>
     </x:row>
     <x:row r="5" ht="25" customHeight="1">
-      <x:c r="A5" s="11"/>
-      <x:c r="B5" s="11"/>
-      <x:c r="C5" s="12"/>
-      <x:c r="D5" s="13"/>
+      <x:c r="A5" s="12"/>
+      <x:c r="B5" s="12"/>
+      <x:c r="C5" s="13"/>
+      <x:c r="D5" s="14"/>
+      <x:c r="E5" s="15"/>
     </x:row>
     <x:row r="6" ht="25" customHeight="1">
-      <x:c r="A6" s="11"/>
-      <x:c r="B6" s="11"/>
-      <x:c r="C6" s="12"/>
-      <x:c r="D6" s="13"/>
+      <x:c r="A6" s="12"/>
+      <x:c r="B6" s="12"/>
+      <x:c r="C6" s="13"/>
+      <x:c r="D6" s="14"/>
+      <x:c r="E6" s="15"/>
     </x:row>
     <x:row r="7" ht="25" customHeight="1">
-      <x:c r="A7" s="11"/>
-      <x:c r="B7" s="11"/>
-      <x:c r="C7" s="12"/>
-      <x:c r="D7" s="13"/>
+      <x:c r="A7" s="12"/>
+      <x:c r="B7" s="12"/>
+      <x:c r="C7" s="13"/>
+      <x:c r="D7" s="14"/>
+      <x:c r="E7" s="15"/>
     </x:row>
     <x:row r="8" ht="25" customHeight="1">
-      <x:c r="A8" s="11"/>
-      <x:c r="B8" s="11"/>
-      <x:c r="C8" s="12"/>
-      <x:c r="D8" s="13"/>
+      <x:c r="A8" s="12"/>
+      <x:c r="B8" s="12"/>
+      <x:c r="C8" s="13"/>
+      <x:c r="D8" s="14"/>
+      <x:c r="E8" s="15"/>
     </x:row>
     <x:row r="9" ht="25" customHeight="1">
-      <x:c r="A9" s="11"/>
-      <x:c r="B9" s="11"/>
-      <x:c r="C9" s="12"/>
-      <x:c r="D9" s="13"/>
+      <x:c r="A9" s="12"/>
+      <x:c r="B9" s="12"/>
+      <x:c r="C9" s="13"/>
+      <x:c r="D9" s="14"/>
+      <x:c r="E9" s="15"/>
     </x:row>
     <x:row r="10" ht="25" customHeight="1">
-      <x:c r="A10" s="11"/>
-      <x:c r="B10" s="11"/>
-      <x:c r="C10" s="12"/>
-      <x:c r="D10" s="13"/>
+      <x:c r="A10" s="12"/>
+      <x:c r="B10" s="12"/>
+      <x:c r="C10" s="13"/>
+      <x:c r="D10" s="14"/>
+      <x:c r="E10" s="15"/>
     </x:row>
     <x:row r="11" ht="25" customHeight="1">
-      <x:c r="A11" s="11"/>
-      <x:c r="B11" s="11"/>
-      <x:c r="C11" s="12"/>
-      <x:c r="D11" s="13"/>
+      <x:c r="A11" s="12"/>
+      <x:c r="B11" s="12"/>
+      <x:c r="C11" s="13"/>
+      <x:c r="D11" s="14"/>
+      <x:c r="E11" s="15"/>
     </x:row>
     <x:row r="12" ht="25" customHeight="1">
-      <x:c r="A12" s="11"/>
-      <x:c r="B12" s="11"/>
-      <x:c r="C12" s="12"/>
-      <x:c r="D12" s="13"/>
+      <x:c r="A12" s="12"/>
+      <x:c r="B12" s="12"/>
+      <x:c r="C12" s="13"/>
+      <x:c r="D12" s="14"/>
+      <x:c r="E12" s="15"/>
     </x:row>
     <x:row r="13" ht="25" customHeight="1">
-      <x:c r="A13" s="11"/>
-      <x:c r="B13" s="11"/>
-      <x:c r="C13" s="12"/>
-      <x:c r="D13" s="13"/>
+      <x:c r="A13" s="12"/>
+      <x:c r="B13" s="12"/>
+      <x:c r="C13" s="13"/>
+      <x:c r="D13" s="14"/>
+      <x:c r="E13" s="15"/>
     </x:row>
     <x:row r="14" ht="25" customHeight="1">
-      <x:c r="A14" s="11"/>
-      <x:c r="B14" s="11"/>
-      <x:c r="C14" s="12"/>
-      <x:c r="D14" s="13"/>
+      <x:c r="A14" s="12"/>
+      <x:c r="B14" s="12"/>
+      <x:c r="C14" s="13"/>
+      <x:c r="D14" s="14"/>
+      <x:c r="E14" s="15"/>
     </x:row>
     <x:row r="15" ht="25" customHeight="1">
-      <x:c r="A15" s="11"/>
-      <x:c r="B15" s="11"/>
-      <x:c r="C15" s="12"/>
-      <x:c r="D15" s="13"/>
+      <x:c r="A15" s="12"/>
+      <x:c r="B15" s="12"/>
+      <x:c r="C15" s="13"/>
+      <x:c r="D15" s="14"/>
+      <x:c r="E15" s="15"/>
     </x:row>
     <x:row r="16" ht="25" customHeight="1">
-      <x:c r="A16" s="11"/>
-      <x:c r="B16" s="11"/>
-      <x:c r="C16" s="12"/>
-      <x:c r="D16" s="13"/>
+      <x:c r="A16" s="12"/>
+      <x:c r="B16" s="12"/>
+      <x:c r="C16" s="13"/>
+      <x:c r="D16" s="14"/>
+      <x:c r="E16" s="15"/>
     </x:row>
     <x:row r="17" ht="25" customHeight="1">
-      <x:c r="A17" s="11"/>
-      <x:c r="B17" s="11"/>
-      <x:c r="C17" s="12"/>
-      <x:c r="D17" s="13"/>
+      <x:c r="A17" s="12"/>
+      <x:c r="B17" s="12"/>
+      <x:c r="C17" s="13"/>
+      <x:c r="D17" s="14"/>
+      <x:c r="E17" s="15"/>
     </x:row>
     <x:row r="18" ht="25" customHeight="1">
-      <x:c r="A18" s="11"/>
-      <x:c r="B18" s="11"/>
-      <x:c r="C18" s="12"/>
-      <x:c r="D18" s="13"/>
+      <x:c r="A18" s="12"/>
+      <x:c r="B18" s="12"/>
+      <x:c r="C18" s="13"/>
+      <x:c r="D18" s="14"/>
+      <x:c r="E18" s="15"/>
     </x:row>
     <x:row r="19" ht="25" customHeight="1">
-      <x:c r="A19" s="11"/>
-      <x:c r="B19" s="11"/>
-      <x:c r="C19" s="12"/>
-      <x:c r="D19" s="13"/>
+      <x:c r="A19" s="12"/>
+      <x:c r="B19" s="12"/>
+      <x:c r="C19" s="13"/>
+      <x:c r="D19" s="14"/>
+      <x:c r="E19" s="15"/>
     </x:row>
     <x:row r="20" ht="25" customHeight="1">
-      <x:c r="A20" s="11"/>
-      <x:c r="B20" s="11"/>
-      <x:c r="C20" s="12"/>
-      <x:c r="D20" s="13"/>
+      <x:c r="A20" s="12"/>
+      <x:c r="B20" s="12"/>
+      <x:c r="C20" s="13"/>
+      <x:c r="D20" s="14"/>
+      <x:c r="E20" s="15"/>
     </x:row>
     <x:row r="21" ht="25" customHeight="1">
-      <x:c r="A21" s="11"/>
-      <x:c r="B21" s="11"/>
-      <x:c r="C21" s="12"/>
-      <x:c r="D21" s="13"/>
+      <x:c r="A21" s="12"/>
+      <x:c r="B21" s="12"/>
+      <x:c r="C21" s="13"/>
+      <x:c r="D21" s="14"/>
+      <x:c r="E21" s="15"/>
     </x:row>
     <x:row r="22" ht="25" customHeight="1">
-      <x:c r="A22" s="11"/>
-      <x:c r="B22" s="11"/>
-      <x:c r="C22" s="12"/>
-      <x:c r="D22" s="13"/>
+      <x:c r="A22" s="12"/>
+      <x:c r="B22" s="12"/>
+      <x:c r="C22" s="13"/>
+      <x:c r="D22" s="14"/>
+      <x:c r="E22" s="15"/>
     </x:row>
     <x:row r="23" ht="25" customHeight="1">
-      <x:c r="A23" s="11"/>
-      <x:c r="B23" s="11"/>
-      <x:c r="C23" s="12"/>
-      <x:c r="D23" s="13"/>
+      <x:c r="A23" s="12"/>
+      <x:c r="B23" s="12"/>
+      <x:c r="C23" s="13"/>
+      <x:c r="D23" s="14"/>
+      <x:c r="E23" s="15"/>
     </x:row>
     <x:row r="24" ht="25" customHeight="1">
-      <x:c r="A24" s="11"/>
-      <x:c r="B24" s="11"/>
-      <x:c r="C24" s="12"/>
-      <x:c r="D24" s="13"/>
+      <x:c r="A24" s="12"/>
+      <x:c r="B24" s="12"/>
+      <x:c r="C24" s="13"/>
+      <x:c r="D24" s="14"/>
+      <x:c r="E24" s="15"/>
     </x:row>
     <x:row r="25" ht="25" customHeight="1">
-      <x:c r="A25" s="11"/>
-      <x:c r="B25" s="11"/>
-      <x:c r="C25" s="12"/>
-      <x:c r="D25" s="13"/>
+      <x:c r="A25" s="12"/>
+      <x:c r="B25" s="12"/>
+      <x:c r="C25" s="13"/>
+      <x:c r="D25" s="14"/>
+      <x:c r="E25" s="15"/>
     </x:row>
     <x:row r="26" ht="25" customHeight="1">
-      <x:c r="A26" s="11"/>
-      <x:c r="B26" s="11"/>
-      <x:c r="C26" s="12"/>
-      <x:c r="D26" s="13"/>
+      <x:c r="A26" s="12"/>
+      <x:c r="B26" s="12"/>
+      <x:c r="C26" s="13"/>
+      <x:c r="D26" s="14"/>
+      <x:c r="E26" s="15"/>
     </x:row>
     <x:row r="27" ht="25" customHeight="1">
-      <x:c r="A27" s="11"/>
-      <x:c r="B27" s="11"/>
-      <x:c r="C27" s="12"/>
-      <x:c r="D27" s="13"/>
+      <x:c r="A27" s="12"/>
+      <x:c r="B27" s="12"/>
+      <x:c r="C27" s="13"/>
+      <x:c r="D27" s="14"/>
+      <x:c r="E27" s="15"/>
     </x:row>
     <x:row r="28" ht="25" customHeight="1">
-      <x:c r="A28" s="11"/>
-      <x:c r="B28" s="11"/>
-      <x:c r="C28" s="12"/>
-      <x:c r="D28" s="13"/>
+      <x:c r="A28" s="12"/>
+      <x:c r="B28" s="12"/>
+      <x:c r="C28" s="13"/>
+      <x:c r="D28" s="14"/>
+      <x:c r="E28" s="15"/>
     </x:row>
     <x:row r="29" ht="25" customHeight="1">
-      <x:c r="A29" s="11"/>
-      <x:c r="B29" s="11"/>
-      <x:c r="C29" s="12"/>
-      <x:c r="D29" s="13"/>
+      <x:c r="A29" s="12"/>
+      <x:c r="B29" s="12"/>
+      <x:c r="C29" s="13"/>
+      <x:c r="D29" s="14"/>
+      <x:c r="E29" s="15"/>
     </x:row>
     <x:row r="30" ht="25" customHeight="1">
-      <x:c r="A30" s="11"/>
-      <x:c r="B30" s="11"/>
-      <x:c r="C30" s="12"/>
-      <x:c r="D30" s="13"/>
+      <x:c r="A30" s="12"/>
+      <x:c r="B30" s="12"/>
+      <x:c r="C30" s="13"/>
+      <x:c r="D30" s="14"/>
+      <x:c r="E30" s="15"/>
     </x:row>
     <x:row r="31" ht="25" customHeight="1">
-      <x:c r="A31" s="11"/>
-      <x:c r="B31" s="11"/>
-      <x:c r="C31" s="12"/>
-      <x:c r="D31" s="13"/>
+      <x:c r="A31" s="12"/>
+      <x:c r="B31" s="12"/>
+      <x:c r="C31" s="13"/>
+      <x:c r="D31" s="14"/>
+      <x:c r="E31" s="15"/>
     </x:row>
     <x:row r="32" ht="25" customHeight="1">
-      <x:c r="A32" s="11"/>
-      <x:c r="B32" s="11"/>
-      <x:c r="C32" s="12"/>
-      <x:c r="D32" s="13"/>
+      <x:c r="A32" s="12"/>
+      <x:c r="B32" s="12"/>
+      <x:c r="C32" s="13"/>
+      <x:c r="D32" s="14"/>
+      <x:c r="E32" s="15"/>
     </x:row>
     <x:row r="33" ht="25" customHeight="1">
-      <x:c r="A33" s="11"/>
-      <x:c r="B33" s="11"/>
-      <x:c r="C33" s="12"/>
-      <x:c r="D33" s="13"/>
+      <x:c r="A33" s="12"/>
+      <x:c r="B33" s="12"/>
+      <x:c r="C33" s="13"/>
+      <x:c r="D33" s="14"/>
+      <x:c r="E33" s="15"/>
     </x:row>
     <x:row r="34" ht="25" customHeight="1">
-      <x:c r="A34" s="11"/>
-      <x:c r="B34" s="11"/>
-      <x:c r="C34" s="12"/>
-      <x:c r="D34" s="13"/>
+      <x:c r="A34" s="12"/>
+      <x:c r="B34" s="12"/>
+      <x:c r="C34" s="13"/>
+      <x:c r="D34" s="14"/>
+      <x:c r="E34" s="15"/>
     </x:row>
     <x:row r="35" ht="25" customHeight="1">
-      <x:c r="A35" s="11"/>
-      <x:c r="B35" s="11"/>
-      <x:c r="C35" s="12"/>
-      <x:c r="D35" s="13"/>
+      <x:c r="A35" s="12"/>
+      <x:c r="B35" s="12"/>
+      <x:c r="C35" s="13"/>
+      <x:c r="D35" s="14"/>
+      <x:c r="E35" s="15"/>
     </x:row>
     <x:row r="36" ht="25" customHeight="1">
-      <x:c r="A36" s="11"/>
-      <x:c r="B36" s="11"/>
-      <x:c r="C36" s="12"/>
-      <x:c r="D36" s="13"/>
+      <x:c r="A36" s="12"/>
+      <x:c r="B36" s="12"/>
+      <x:c r="C36" s="13"/>
+      <x:c r="D36" s="14"/>
+      <x:c r="E36" s="15"/>
     </x:row>
     <x:row r="37" ht="25" customHeight="1">
-      <x:c r="A37" s="11"/>
-      <x:c r="B37" s="11"/>
-      <x:c r="C37" s="12"/>
-      <x:c r="D37" s="13"/>
+      <x:c r="A37" s="12"/>
+      <x:c r="B37" s="12"/>
+      <x:c r="C37" s="13"/>
+      <x:c r="D37" s="14"/>
+      <x:c r="E37" s="15"/>
     </x:row>
     <x:row r="38" ht="25" customHeight="1">
-      <x:c r="A38" s="11"/>
-      <x:c r="B38" s="11"/>
-      <x:c r="C38" s="12"/>
-      <x:c r="D38" s="13"/>
+      <x:c r="A38" s="12"/>
+      <x:c r="B38" s="12"/>
+      <x:c r="C38" s="13"/>
+      <x:c r="D38" s="14"/>
+      <x:c r="E38" s="15"/>
     </x:row>
     <x:row r="39" ht="25" customHeight="1">
-      <x:c r="A39" s="11"/>
-      <x:c r="B39" s="11"/>
-      <x:c r="C39" s="12"/>
-      <x:c r="D39" s="13"/>
+      <x:c r="A39" s="12"/>
+      <x:c r="B39" s="12"/>
+      <x:c r="C39" s="13"/>
+      <x:c r="D39" s="14"/>
+      <x:c r="E39" s="15"/>
     </x:row>
     <x:row r="40" ht="25" customHeight="1">
-      <x:c r="A40" s="11"/>
-      <x:c r="B40" s="11"/>
-      <x:c r="C40" s="12"/>
-      <x:c r="D40" s="13"/>
+      <x:c r="A40" s="12"/>
+      <x:c r="B40" s="12"/>
+      <x:c r="C40" s="13"/>
+      <x:c r="D40" s="14"/>
+      <x:c r="E40" s="15"/>
     </x:row>
     <x:row r="41" ht="25" customHeight="1">
-      <x:c r="A41" s="11"/>
-      <x:c r="B41" s="11"/>
-      <x:c r="C41" s="12"/>
-      <x:c r="D41" s="13"/>
+      <x:c r="A41" s="12"/>
+      <x:c r="B41" s="12"/>
+      <x:c r="C41" s="13"/>
+      <x:c r="D41" s="14"/>
+      <x:c r="E41" s="15"/>
     </x:row>
     <x:row r="42" ht="25" customHeight="1">
-      <x:c r="A42" s="11"/>
-      <x:c r="B42" s="11"/>
-      <x:c r="C42" s="12"/>
-      <x:c r="D42" s="13"/>
+      <x:c r="A42" s="12"/>
+      <x:c r="B42" s="12"/>
+      <x:c r="C42" s="13"/>
+      <x:c r="D42" s="14"/>
+      <x:c r="E42" s="15"/>
     </x:row>
     <x:row r="43" ht="25" customHeight="1">
-      <x:c r="A43" s="11"/>
-      <x:c r="B43" s="11"/>
-      <x:c r="C43" s="12"/>
-      <x:c r="D43" s="13"/>
+      <x:c r="A43" s="12"/>
+      <x:c r="B43" s="12"/>
+      <x:c r="C43" s="13"/>
+      <x:c r="D43" s="14"/>
+      <x:c r="E43" s="15"/>
     </x:row>
     <x:row r="44" ht="25" customHeight="1">
-      <x:c r="A44" s="11"/>
-      <x:c r="B44" s="11"/>
-      <x:c r="C44" s="12"/>
-      <x:c r="D44" s="13"/>
+      <x:c r="A44" s="12"/>
+      <x:c r="B44" s="12"/>
+      <x:c r="C44" s="13"/>
+      <x:c r="D44" s="14"/>
+      <x:c r="E44" s="15"/>
     </x:row>
     <x:row r="45" ht="25" customHeight="1">
-      <x:c r="A45" s="11"/>
-      <x:c r="B45" s="11"/>
-      <x:c r="C45" s="12"/>
-      <x:c r="D45" s="13"/>
+      <x:c r="A45" s="12"/>
+      <x:c r="B45" s="12"/>
+      <x:c r="C45" s="13"/>
+      <x:c r="D45" s="14"/>
+      <x:c r="E45" s="15"/>
     </x:row>
     <x:row r="46" ht="25" customHeight="1">
-      <x:c r="A46" s="11"/>
-      <x:c r="B46" s="11"/>
-      <x:c r="C46" s="12"/>
-      <x:c r="D46" s="13"/>
+      <x:c r="A46" s="12"/>
+      <x:c r="B46" s="12"/>
+      <x:c r="C46" s="13"/>
+      <x:c r="D46" s="14"/>
+      <x:c r="E46" s="15"/>
     </x:row>
     <x:row r="47" ht="25" customHeight="1">
-      <x:c r="A47" s="11"/>
-      <x:c r="B47" s="11"/>
-      <x:c r="C47" s="12"/>
-      <x:c r="D47" s="13"/>
+      <x:c r="A47" s="12"/>
+      <x:c r="B47" s="12"/>
+      <x:c r="C47" s="13"/>
+      <x:c r="D47" s="14"/>
+      <x:c r="E47" s="15"/>
     </x:row>
     <x:row r="48" ht="25" customHeight="1">
-      <x:c r="A48" s="11"/>
-      <x:c r="B48" s="11"/>
-      <x:c r="C48" s="12"/>
-      <x:c r="D48" s="13"/>
+      <x:c r="A48" s="12"/>
+      <x:c r="B48" s="12"/>
+      <x:c r="C48" s="13"/>
+      <x:c r="D48" s="14"/>
+      <x:c r="E48" s="15"/>
     </x:row>
     <x:row r="49" ht="25" customHeight="1">
-      <x:c r="A49" s="11"/>
-      <x:c r="B49" s="11"/>
-      <x:c r="C49" s="12"/>
-      <x:c r="D49" s="13"/>
+      <x:c r="A49" s="12"/>
+      <x:c r="B49" s="12"/>
+      <x:c r="C49" s="13"/>
+      <x:c r="D49" s="14"/>
+      <x:c r="E49" s="15"/>
     </x:row>
     <x:row r="50" ht="25" customHeight="1">
-      <x:c r="A50" s="11"/>
-      <x:c r="B50" s="11"/>
-      <x:c r="C50" s="12"/>
-      <x:c r="D50" s="13"/>
+      <x:c r="A50" s="12"/>
+      <x:c r="B50" s="12"/>
+      <x:c r="C50" s="13"/>
+      <x:c r="D50" s="14"/>
+      <x:c r="E50" s="15"/>
     </x:row>
     <x:row r="51" ht="25" customHeight="1">
-      <x:c r="A51" s="11"/>
-      <x:c r="B51" s="11"/>
-      <x:c r="C51" s="12"/>
-      <x:c r="D51" s="13"/>
+      <x:c r="A51" s="12"/>
+      <x:c r="B51" s="12"/>
+      <x:c r="C51" s="13"/>
+      <x:c r="D51" s="14"/>
+      <x:c r="E51" s="15"/>
     </x:row>
     <x:row r="52" ht="25" customHeight="1">
-      <x:c r="A52" s="11"/>
-      <x:c r="B52" s="11"/>
-      <x:c r="C52" s="12"/>
-      <x:c r="D52" s="13"/>
+      <x:c r="A52" s="12"/>
+      <x:c r="B52" s="12"/>
+      <x:c r="C52" s="13"/>
+      <x:c r="D52" s="14"/>
+      <x:c r="E52" s="15"/>
     </x:row>
     <x:row r="53" ht="25" customHeight="1">
-      <x:c r="A53" s="11"/>
-      <x:c r="B53" s="11"/>
-      <x:c r="C53" s="12"/>
-      <x:c r="D53" s="13"/>
+      <x:c r="A53" s="12"/>
+      <x:c r="B53" s="12"/>
+      <x:c r="C53" s="13"/>
+      <x:c r="D53" s="14"/>
+      <x:c r="E53" s="15"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
